--- a/resources/report/60/95/rpt_6095300.xlsx
+++ b/resources/report/60/95/rpt_6095300.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project's Resources\gsf20\resources\report\60\95\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project's Resources\einvoicevn.com\resources\report\60\95\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -268,7 +268,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -341,6 +345,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -386,11 +397,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -421,8 +433,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 18" xfId="1"/>
   </cellStyles>
@@ -719,16 +735,16 @@
     <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" customWidth="1"/>
     <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10" customWidth="1"/>
     <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.140625" customWidth="1"/>
+    <col min="22" max="22" width="9.5703125" customWidth="1"/>
     <col min="23" max="23" width="11.28515625" customWidth="1"/>
-    <col min="24" max="24" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.7109375" customWidth="1"/>
     <col min="25" max="25" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="22.42578125" bestFit="1" customWidth="1"/>
@@ -989,31 +1005,31 @@
       <c r="O3" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="14" t="s">
         <v>48</v>
       </c>
       <c r="R3" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="S3" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="T3" s="12" t="s">
+      <c r="T3" s="14" t="s">
         <v>51</v>
       </c>
       <c r="U3" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="V3" s="12" t="s">
+      <c r="V3" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="W3" s="12" t="s">
+      <c r="W3" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="X3" s="12" t="s">
+      <c r="X3" s="14" t="s">
         <v>60</v>
       </c>
       <c r="Y3" s="12" t="s">

--- a/resources/report/60/95/rpt_6095300.xlsx
+++ b/resources/report/60/95/rpt_6095300.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
   <si>
     <t>STT</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>TCHDON</t>
+  </si>
+  <si>
+    <t>FILE_NAME</t>
   </si>
 </sst>
 </file>
@@ -270,7 +273,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -433,7 +436,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -965,7 +968,9 @@
       <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10"/>
+      <c r="B3" s="10" t="s">
+        <v>67</v>
+      </c>
       <c r="C3" s="9" t="s">
         <v>36</v>
       </c>

--- a/resources/report/60/95/rpt_6095300.xlsx
+++ b/resources/report/60/95/rpt_6095300.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="70">
   <si>
     <t>STT</t>
   </si>
@@ -265,6 +265,12 @@
   </si>
   <si>
     <t>FILE_NAME</t>
+  </si>
+  <si>
+    <t>Cấu trúc file nguyên vẹn</t>
+  </si>
+  <si>
+    <t>FILE_INTERGRITY</t>
   </si>
 </sst>
 </file>
@@ -376,7 +382,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -399,13 +405,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -439,6 +456,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -721,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -756,7 +774,7 @@
     <col min="30" max="34" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="1" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" s="1" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -859,8 +877,11 @@
       <c r="AH1" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AI1" s="3" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -963,8 +984,11 @@
       <c r="AH2" s="4">
         <v>34</v>
       </c>
+      <c r="AI2" s="15">
+        <v>35</v>
+      </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
@@ -1063,8 +1087,11 @@
         <v>63</v>
       </c>
       <c r="AH3" s="12"/>
+      <c r="AI3" s="12" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1107,8 +1134,9 @@
       <c r="AF4" s="8"/>
       <c r="AG4" s="8"/>
       <c r="AH4" s="8"/>
+      <c r="AI4" s="8"/>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -1116,7 +1144,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>32</v>
       </c>

--- a/resources/report/60/95/rpt_6095300.xlsx
+++ b/resources/report/60/95/rpt_6095300.xlsx
@@ -270,7 +270,7 @@
     <t>Cấu trúc file nguyên vẹn</t>
   </si>
   <si>
-    <t>FILE_INTERGRITY</t>
+    <t>FILE_INTEGRITY</t>
   </si>
 </sst>
 </file>
